--- a/reports/devops-juniors-israel-2026-W29.xlsx
+++ b/reports/devops-juniors-israel-2026-W29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-13T09:46:17</t>
+    <t xml:space="preserve">2026-07-14T08:25:28</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -181,703 +181,793 @@
     <t xml:space="preserve">2026-05-25</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HelpDesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application Infrastructure Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-support-engineer-at-comblack-4440032325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Technical Support Specialist (36859)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technical-support-specialist-36859-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439731247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist with Hebrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squaretalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-with-hebrew-at-squaretalk-4430457260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Voyager Labs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-voyager-labs-4420475324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
   </si>
   <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-anecdotes-4437847270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP, Cloud (any), Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-system-administrator-at-skai-4432646199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HelpDesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist with Hebrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-with-hebrew-at-squaretalk-4430457260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4435990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (Contractor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards Lifesciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support start pozision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MalamTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-start-pozision-at-malamteam-4437276599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Site Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW System Engineer for Naval Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-system-engineer-for-naval-systems-at-elbit-systems-israel-4437266128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (36097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439712914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help desk</t>
   </si>
   <si>
     <t xml:space="preserve">Genie</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator (10156)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bynet Data Communications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-10156-at-bynet-data-communications-4437208810</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4435990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-sqlink-group-4434512605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-dialog-4433929051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Site Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
   </si>
   <si>
     <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
@@ -889,16 +979,10 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439712914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WalkMe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -910,34 +994,43 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
@@ -946,10 +1039,10 @@
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
     <t xml:space="preserve">CI/CD</t>
@@ -958,28 +1051,16 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1140,7 +1221,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -1156,7 +1237,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1164,7 +1245,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10">
@@ -1246,7 +1327,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
@@ -1254,7 +1335,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1262,7 +1343,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1296,7 +1377,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29">
@@ -1316,7 +1397,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1433,25 +1514,25 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="3">
-        <v>88</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1459,13 +1540,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1474,16 +1555,16 @@
         <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1491,7 +1572,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>67</v>
@@ -1500,22 +1581,22 @@
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1523,31 +1604,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1555,19 +1636,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>79</v>
@@ -1593,7 +1674,7 @@
         <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>28</v>
@@ -1619,31 +1700,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1651,31 +1732,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1683,13 +1764,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
@@ -1698,16 +1779,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -1715,10 +1796,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>45</v>
@@ -1730,16 +1811,16 @@
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1747,31 +1828,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -1779,31 +1860,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1811,31 +1892,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -1843,31 +1924,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
@@ -1875,31 +1956,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19">
@@ -1907,31 +1988,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -1939,31 +2020,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21">
@@ -1971,31 +2052,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -2003,31 +2084,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -2035,31 +2116,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24">
@@ -2067,31 +2148,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25">
@@ -2099,31 +2180,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26">
@@ -2131,31 +2212,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2208,7 +2289,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2223,22 +2304,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2261,7 +2342,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2273,7 +2354,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -2296,7 +2377,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2308,7 +2389,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -2319,42 +2400,42 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="3">
-        <v>88</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K4" s="3">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2363,27 +2444,27 @@
         <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>67</v>
@@ -2392,86 +2473,86 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2483,7 +2564,7 @@
         <v>81</v>
       </c>
       <c r="K8" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2494,7 +2575,7 @@
         <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>28</v>
@@ -2506,7 +2587,7 @@
         <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2518,39 +2599,39 @@
         <v>86</v>
       </c>
       <c r="K9" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
         <v>12</v>
@@ -2558,48 +2639,48 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3">
-        <v>59</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
@@ -2608,30 +2689,30 @@
         <v>47</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="K12" s="3">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>45</v>
@@ -2643,649 +2724,649 @@
         <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K13" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="K15" s="3">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K16" s="3">
-        <v>54</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K17" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="K20" s="3">
-        <v>13</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="K23" s="3">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>117</v>
+        <v>81</v>
       </c>
       <c r="K25" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="K26" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>173</v>
+        <v>60</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
+        <v>20</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="K27" s="3">
         <v>27</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K27" s="3">
-        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="K28" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="K29" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>186</v>
+        <v>153</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="K30" s="3">
-        <v>59</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>51</v>
+        <v>109</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3293,48 +3374,48 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="K32" s="3">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
@@ -3343,33 +3424,33 @@
         <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K33" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
@@ -3378,68 +3459,68 @@
         <v>13</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>206</v>
+        <v>59</v>
       </c>
       <c r="K34" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>55</v>
+        <v>211</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3">
         <v>13</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="K35" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>210</v>
+        <v>125</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>211</v>
+        <v>126</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
@@ -3448,68 +3529,68 @@
         <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="K36" s="3">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>57</v>
+        <v>219</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
@@ -3518,33 +3599,33 @@
         <v>10</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>206</v>
+        <v>59</v>
       </c>
       <c r="K38" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3553,33 +3634,33 @@
         <v>10</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="K39" s="3">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>76</v>
+        <v>232</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>25</v>
@@ -3588,33 +3669,33 @@
         <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="K40" s="3">
-        <v>50</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3623,33 +3704,33 @@
         <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>141</v>
+        <v>242</v>
       </c>
       <c r="K41" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
@@ -3658,33 +3739,33 @@
         <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K42" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
@@ -3693,103 +3774,103 @@
         <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>131</v>
+        <v>249</v>
       </c>
       <c r="K43" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>224</v>
+        <v>72</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>243</v>
+        <v>74</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>206</v>
+        <v>59</v>
       </c>
       <c r="K44" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>247</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E45" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>251</v>
+        <v>151</v>
       </c>
       <c r="K45" s="3">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3798,33 +3879,33 @@
         <v>6</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K46" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3833,313 +3914,313 @@
         <v>6</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>166</v>
+        <v>81</v>
       </c>
       <c r="K47" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="K48" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>271</v>
+        <v>151</v>
       </c>
       <c r="K49" s="3">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>224</v>
+        <v>277</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>126</v>
+        <v>281</v>
       </c>
       <c r="K51" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>118</v>
+        <v>282</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="K52" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>159</v>
+        <v>289</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>126</v>
+        <v>292</v>
       </c>
       <c r="K53" s="3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E54" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="K54" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>289</v>
+        <v>208</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K55" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4148,33 +4229,33 @@
         <v>3</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K56" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>55</v>
+        <v>303</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>293</v>
+        <v>183</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>25</v>
@@ -4183,26 +4264,234 @@
         <v>3</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="K57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K60" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K61" s="3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K62" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K63" s="3">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:K63"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4260,6 +4549,12 @@
     <hyperlink ref="I55" r:id="rId54"/>
     <hyperlink ref="I56" r:id="rId55"/>
     <hyperlink ref="I57" r:id="rId56"/>
+    <hyperlink ref="I58" r:id="rId57"/>
+    <hyperlink ref="I59" r:id="rId58"/>
+    <hyperlink ref="I60" r:id="rId59"/>
+    <hyperlink ref="I61" r:id="rId60"/>
+    <hyperlink ref="I62" r:id="rId61"/>
+    <hyperlink ref="I63" r:id="rId62"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4267,7 +4562,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
@@ -4290,10 +4585,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4301,56 +4596,56 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
@@ -4359,128 +4654,128 @@
         <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>224</v>
+        <v>261</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>284</v>
+        <v>208</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4508,178 +4803,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>323</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>324</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="B2" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>298</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B3" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="B4" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>300</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>301</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="B6" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>303</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>205</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>306</v>
+        <v>334</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>200</v>
+        <v>308</v>
       </c>
       <c r="B9" s="3">
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>307</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>308</v>
+        <v>336</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>309</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>311</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>314</v>
+        <v>341</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>315</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>321</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4699,10 +4994,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>323</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2">
@@ -4710,10 +5005,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
@@ -4721,10 +5016,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>325</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4">
@@ -4732,10 +5027,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5">
@@ -4746,7 +5041,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>327</v>
+        <v>354</v>
       </c>
     </row>
     <row r="6">
@@ -4757,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>328</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4778,13 +5073,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>331</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
@@ -4795,7 +5090,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4804,22 +5099,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W29.xlsx
+++ b/reports/devops-juniors-israel-2026-W29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-14T08:25:28</t>
+    <t xml:space="preserve">2026-07-15T08:31:45</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -145,6 +145,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior AI SRE Developer</t>
   </si>
   <si>
@@ -163,24 +181,6 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior IT DevOps Engineer - Temporary Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobileye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-it-devops-engineer-temporary-position-at-mobileye-4417802849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-25</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -196,6 +196,24 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator</t>
   </si>
   <si>
@@ -214,829 +232,859 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+    <t xml:space="preserve">Infrastructure System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peak Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segment IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-segment-it-4438049762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAREL LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist with Hebrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Squaretalk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-with-hebrew-at-squaretalk-4430457260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">טכנאי/ת Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4435990421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
   </si>
   <si>
     <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HelpDesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/helpdesk-at-abra-4436085074</t>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dragontail Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On-Site Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LabOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (36097)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439712914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-06</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Application Infrastructure Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/application-infrastructure-support-engineer-at-comblack-4440032325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Technical Support Specialist (36859)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technical-support-specialist-36859-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439731247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist with Hebrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-with-hebrew-at-squaretalk-4430457260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross River</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cross-river-4408813327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4435990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (Contractor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwards Lifesciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support start pozision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MalamTeam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-start-pozision-at-malamteam-4437276599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Site Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW System Engineer for Naval Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-system-engineer-for-naval-systems-at-elbit-systems-israel-4437266128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439712914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4410001855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">AWS</t>
@@ -1221,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -1229,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1237,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -1245,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10">
@@ -1327,7 +1375,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -1335,7 +1383,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1377,7 +1425,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
@@ -1453,7 +1501,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1485,7 +1533,7 @@
         <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1514,7 +1562,7 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1552,7 +1600,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>63</v>
@@ -1581,10 +1629,10 @@
         <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1610,25 +1658,25 @@
         <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3">
+        <v>76</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="3">
-        <v>68</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1636,19 +1684,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>79</v>
@@ -1660,7 +1708,7 @@
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1668,31 +1716,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>68</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="3">
-        <v>57</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1700,31 +1748,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11">
@@ -1732,31 +1780,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3">
+        <v>57</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="3">
-        <v>52</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1764,31 +1812,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="3">
+        <v>56</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>47</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -1796,31 +1844,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1828,31 +1876,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
@@ -1860,31 +1908,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>51</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>32</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="16">
@@ -1892,31 +1940,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -1924,31 +1972,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18">
@@ -1956,31 +2004,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
@@ -1988,31 +2036,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -2020,31 +2068,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
@@ -2052,31 +2100,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22">
@@ -2084,31 +2132,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -2116,31 +2164,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24">
@@ -2148,31 +2196,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25">
@@ -2180,31 +2228,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26">
@@ -2212,31 +2260,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2289,7 +2337,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2304,22 +2352,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
@@ -2333,7 +2381,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2342,7 +2390,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2354,7 +2402,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -2368,7 +2416,7 @@
         <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2377,7 +2425,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2389,7 +2437,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2400,7 +2448,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2412,7 +2460,7 @@
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2424,7 +2472,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -2441,13 +2489,13 @@
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2459,7 +2507,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -2473,16 +2521,16 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2494,7 +2542,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2505,54 +2553,54 @@
         <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="3">
+        <v>76</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>68</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="K7" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2561,7 +2609,7 @@
         <v>80</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -2569,1679 +2617,1679 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>68</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="3">
-        <v>57</v>
-      </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="K9" s="3">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="K10" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="3">
+        <v>57</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="3">
-        <v>52</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="K11" s="3">
-        <v>14</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3">
+        <v>56</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>47</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="K12" s="3">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="K13" s="3">
-        <v>56</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K14" s="3">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>51</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>32</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K15" s="3">
-        <v>33</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="K16" s="3">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K17" s="3">
-        <v>15</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="K18" s="3">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="K19" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="K20" s="3">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>148</v>
+        <v>62</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="K21" s="3">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="K22" s="3">
-        <v>8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="K23" s="3">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="K24" s="3">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="K26" s="3">
-        <v>60</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K27" s="3">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>182</v>
+        <v>55</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>81</v>
+        <v>180</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="K30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>199</v>
+        <v>157</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K32" s="3">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>203</v>
+        <v>132</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K33" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="K34" s="3">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>211</v>
+        <v>66</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="3">
+        <v>20</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E35" s="3">
-        <v>13</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>54</v>
+        <v>209</v>
       </c>
       <c r="K35" s="3">
-        <v>50</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="K36" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>219</v>
+        <v>102</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="K37" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>224</v>
+        <v>146</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="K38" s="3">
-        <v>51</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E39" s="3">
+        <v>13</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>10</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="K39" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>233</v>
+        <v>151</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>237</v>
+        <v>59</v>
       </c>
       <c r="K40" s="3">
-        <v>29</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>239</v>
+        <v>151</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>242</v>
+        <v>59</v>
       </c>
       <c r="K41" s="3">
-        <v>2</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>244</v>
+        <v>151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="K42" s="3">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>148</v>
+        <v>238</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="K43" s="3">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>72</v>
+        <v>242</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="K44" s="3">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>254</v>
+        <v>128</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="K45" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>258</v>
+        <v>151</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E46" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E47" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>71</v>
+        <v>263</v>
       </c>
       <c r="K48" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>271</v>
+        <v>62</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>151</v>
+        <v>268</v>
       </c>
       <c r="K49" s="3">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>59</v>
+        <v>274</v>
       </c>
       <c r="K50" s="3">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>281</v>
+        <v>59</v>
       </c>
       <c r="K51" s="3">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="3">
-        <v>4</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="K53" s="3">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>148</v>
+        <v>284</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>199</v>
+        <v>238</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>81</v>
+        <v>189</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="K56" s="3">
         <v>1</v>
@@ -4249,37 +4297,37 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E57" s="3">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>298</v>
-      </c>
       <c r="G57" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>304</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
@@ -4287,66 +4335,66 @@
         <v>305</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>183</v>
+        <v>306</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>123</v>
+        <v>309</v>
       </c>
       <c r="K58" s="3">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="K59" s="3">
         <v>1</v>
@@ -4354,13 +4402,13 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>217</v>
+        <v>314</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4369,33 +4417,33 @@
         <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>92</v>
+        <v>175</v>
       </c>
       <c r="K60" s="3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>313</v>
+        <v>259</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4404,33 +4452,33 @@
         <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>317</v>
+        <v>175</v>
       </c>
       <c r="K61" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4439,59 +4487,201 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K62" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>212</v>
+        <v>102</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E63" s="3">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>312</v>
+      </c>
       <c r="G63" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3">
+        <v>3</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="J63" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="K63" s="3">
-        <v>50</v>
+      <c r="G64" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K64" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="3">
+        <v>3</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="J65" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="K65" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="K67" s="3">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K63"/>
+  <autoFilter ref="A1:K67"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4555,6 +4745,10 @@
     <hyperlink ref="I61" r:id="rId60"/>
     <hyperlink ref="I62" r:id="rId61"/>
     <hyperlink ref="I63" r:id="rId62"/>
+    <hyperlink ref="I64" r:id="rId63"/>
+    <hyperlink ref="I65" r:id="rId64"/>
+    <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4562,9 +4756,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4585,10 +4779,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4596,190 +4790,167 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>138</v>
+        <v>79</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>184</v>
+        <v>129</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>185</v>
+        <v>130</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>193</v>
+        <v>131</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>195</v>
+        <v>134</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>258</v>
+        <v>132</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>259</v>
+        <v>199</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4788,7 +4959,6 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4803,178 +4973,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>285</v>
+        <v>345</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>205</v>
+        <v>307</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>308</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>336</v>
+        <v>252</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>315</v>
+        <v>353</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="B15" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B16" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -4994,10 +5164,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -5005,10 +5175,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
     </row>
     <row r="3">
@@ -5016,10 +5186,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4">
@@ -5030,7 +5200,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
     </row>
     <row r="5">
@@ -5041,7 +5211,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -5052,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5073,13 +5243,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5090,7 +5260,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5099,22 +5269,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W29.xlsx
+++ b/reports/devops-juniors-israel-2026-W29.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-15T08:31:45</t>
+    <t xml:space="preserve">2026-07-16T08:29:36</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -232,456 +232,495 @@
     <t xml:space="preserve">2026-06-28</t>
   </si>
   <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, CI/CD, Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4437265103</t>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anecdotes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IOT student tester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motorola Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist - Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gambit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GTM Engineer - Student Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oak - Identity Security OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gtm-engineer-student-role-at-oak-identity-security-os-4441425975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peak Innovation</t>
+    <t xml:space="preserve">Data Science Student for AI Solutions Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-science-student-for-ai-solutions-group-at-intel-4439417170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - JB-651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
   </si>
   <si>
     <t xml:space="preserve">Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-peak-innovation-4431041046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-segment-it-4438049762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-09</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMAREL LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-amarel-ltd-4428035454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist with Hebrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Squaretalk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-with-hebrew-at-squaretalk-4430457260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
   </si>
   <si>
@@ -697,9 +736,6 @@
     <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avionics Systems Engineering Student</t>
   </si>
   <si>
@@ -715,31 +751,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
   </si>
   <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">טכנאי/ת Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashdod, South District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-help-desk-at-genie-4427161897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Support Technician</t>
@@ -757,18 +775,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
   </si>
   <si>
@@ -793,180 +799,192 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (Contractor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards Lifesciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW System Engineer for Naval Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-system-engineer-for-naval-systems-at-elbit-systems-israel-4437266128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
-    <t xml:space="preserve">ONE Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-one-technologies-4435990421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Agent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dragontail Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-agent-at-dragontail-systems-4434570509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On-Site Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LabOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/on-site-technical-support-specialist-at-labos-4434814951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
     <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
   </si>
   <si>
@@ -976,61 +994,43 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+    <t xml:space="preserve">IT Support Specialist (Help Desk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octally Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-help-desk-at-octally-integration-4438080376</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Technician (36097)</t>
   </si>
   <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439712914</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Technical Support Representatives (Private &amp; Business Clients)</t>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">‫Technical Support Representative</t>
   </si>
   <si>
     <t xml:space="preserve">JobsSeek</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representatives-private-business-clients-at-jobsseek-4430394705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representative-at-jobsseek-4430394705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1048,37 +1048,43 @@
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
   </si>
   <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
     <t xml:space="preserve">Virtualization</t>
@@ -1087,22 +1093,16 @@
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -1269,7 +1269,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -1277,7 +1277,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1293,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10">
@@ -1383,7 +1383,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -1391,7 +1391,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29">
@@ -1652,13 +1652,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -1667,16 +1667,16 @@
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
@@ -1684,31 +1684,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -1728,7 +1728,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>83</v>
@@ -1748,31 +1748,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -1780,19 +1780,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>91</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>92</v>
@@ -1818,25 +1818,25 @@
         <v>96</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="3">
+        <v>57</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>56</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1844,7 +1844,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>101</v>
@@ -1885,7 +1885,7 @@
         <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
         <v>52</v>
@@ -1900,7 +1900,7 @@
         <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -1908,19 +1908,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>112</v>
@@ -1940,31 +1940,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>117</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1975,28 +1975,28 @@
         <v>81</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -2004,31 +2004,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2036,22 +2036,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" s="3">
+        <v>47</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F19" s="3">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -2060,7 +2060,7 @@
         <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20">
@@ -2068,16 +2068,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
         <v>44</v>
@@ -2086,13 +2086,13 @@
         <v>134</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
@@ -2100,13 +2100,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -2115,16 +2115,16 @@
         <v>44</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22">
@@ -2132,7 +2132,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>61</v>
@@ -2147,13 +2147,13 @@
         <v>44</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>54</v>
@@ -2164,19 +2164,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>147</v>
@@ -2228,19 +2228,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>158</v>
@@ -2252,7 +2252,7 @@
         <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
@@ -2260,31 +2260,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2323,7 +2323,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2337,7 +2337,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2352,22 +2352,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2">
@@ -2390,7 +2390,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2402,7 +2402,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -2425,7 +2425,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2437,7 +2437,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -2460,7 +2460,7 @@
         <v>57</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2472,7 +2472,7 @@
         <v>59</v>
       </c>
       <c r="K4" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -2495,7 +2495,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2507,7 +2507,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -2530,7 +2530,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2542,18 +2542,18 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
@@ -2562,57 +2562,57 @@
         <v>76</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2629,13 +2629,13 @@
         <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -2647,39 +2647,39 @@
         <v>85</v>
       </c>
       <c r="K9" s="3">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K10" s="3">
         <v>1</v>
@@ -2687,25 +2687,25 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -2717,7 +2717,7 @@
         <v>94</v>
       </c>
       <c r="K11" s="3">
-        <v>61</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2728,36 +2728,36 @@
         <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3">
+        <v>57</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>56</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="K12" s="3">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>101</v>
@@ -2775,7 +2775,7 @@
         <v>103</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
@@ -2787,7 +2787,7 @@
         <v>105</v>
       </c>
       <c r="K13" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -2801,7 +2801,7 @@
         <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
         <v>52</v>
@@ -2810,7 +2810,7 @@
         <v>108</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
@@ -2819,33 +2819,33 @@
         <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>112</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
@@ -2857,42 +2857,42 @@
         <v>114</v>
       </c>
       <c r="K15" s="3">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>62</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>117</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>118</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="K16" s="3">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -2900,92 +2900,92 @@
         <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="K18" s="3">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3">
+        <v>47</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="3">
-        <v>44</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="G19" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -2994,24 +2994,24 @@
         <v>130</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
         <v>44</v>
@@ -3020,30 +3020,30 @@
         <v>134</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -3052,27 +3052,27 @@
         <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="K21" s="3">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>61</v>
@@ -3087,45 +3087,45 @@
         <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>54</v>
       </c>
       <c r="K22" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>147</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
@@ -3137,7 +3137,7 @@
         <v>149</v>
       </c>
       <c r="K23" s="3">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -3160,7 +3160,7 @@
         <v>153</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
@@ -3172,30 +3172,30 @@
         <v>155</v>
       </c>
       <c r="K24" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>66</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>158</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
@@ -3204,115 +3204,115 @@
         <v>159</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>105</v>
+        <v>160</v>
       </c>
       <c r="K25" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>171</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="K27" s="3">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>177</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>177</v>
+        <v>62</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="K28" s="3">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -3323,19 +3323,19 @@
         <v>182</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>183</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
@@ -3344,45 +3344,45 @@
         <v>184</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="K29" s="3">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="K30" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -3393,168 +3393,168 @@
         <v>191</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>62</v>
+        <v>192</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="K31" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>195</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>157</v>
+        <v>196</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E32" s="3">
+        <v>28</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K32" s="3">
         <v>24</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>133</v>
+        <v>62</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="K33" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K34" s="3">
-        <v>61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>66</v>
+        <v>209</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="K35" s="3">
         <v>28</v>
@@ -3562,188 +3562,188 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>45</v>
+        <v>215</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>175</v>
+        <v>99</v>
       </c>
       <c r="K36" s="3">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>189</v>
+        <v>90</v>
       </c>
       <c r="K37" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>146</v>
+        <v>223</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="K38" s="3">
-        <v>1</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="K39" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>151</v>
+        <v>214</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>59</v>
+        <v>234</v>
       </c>
       <c r="K40" s="3">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>151</v>
+        <v>236</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>152</v>
+        <v>237</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>27</v>
@@ -3752,33 +3752,33 @@
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="K41" s="3">
-        <v>52</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>152</v>
+        <v>241</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>27</v>
@@ -3787,68 +3787,68 @@
         <v>13</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>235</v>
+        <v>59</v>
       </c>
       <c r="K42" s="3">
-        <v>37</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>237</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>238</v>
+        <v>152</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
         <v>13</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>241</v>
+        <v>59</v>
       </c>
       <c r="K43" s="3">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>243</v>
+        <v>191</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>244</v>
+        <v>192</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
@@ -3857,33 +3857,33 @@
         <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>76</v>
+        <v>204</v>
       </c>
       <c r="K44" s="3">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3892,33 +3892,33 @@
         <v>13</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="K45" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>26</v>
@@ -3927,33 +3927,33 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>227</v>
+        <v>80</v>
       </c>
       <c r="K46" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3962,33 +3962,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>59</v>
       </c>
       <c r="K47" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>146</v>
+        <v>62</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3997,33 +3997,33 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K48" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>62</v>
+        <v>268</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>25</v>
@@ -4032,33 +4032,33 @@
         <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K49" s="3">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>271</v>
+        <v>102</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
@@ -4067,22 +4067,22 @@
         <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>274</v>
+        <v>85</v>
       </c>
       <c r="K50" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4105,7 +4105,7 @@
         <v>276</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
@@ -4117,42 +4117,42 @@
         <v>59</v>
       </c>
       <c r="K51" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F52" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="K52" s="3">
-        <v>52</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -4163,42 +4163,42 @@
         <v>283</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F53" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="J53" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="K53" s="3">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4207,33 +4207,33 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="K54" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>25</v>
@@ -4242,33 +4242,33 @@
         <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="K55" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>25</v>
@@ -4277,33 +4277,33 @@
         <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K56" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>27</v>
@@ -4312,33 +4312,33 @@
         <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="K57" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>26</v>
@@ -4347,33 +4347,33 @@
         <v>4</v>
       </c>
       <c r="F58" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J58" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>309</v>
-      </c>
       <c r="K58" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>311</v>
+        <v>151</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>157</v>
+        <v>309</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>26</v>
@@ -4382,33 +4382,33 @@
         <v>4</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K59" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>284</v>
+        <v>139</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4417,33 +4417,33 @@
         <v>3</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="K60" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>259</v>
+        <v>315</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4452,33 +4452,33 @@
         <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="G61" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>319</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K61" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="C62" s="3" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4487,33 +4487,33 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>76</v>
+        <v>185</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4522,33 +4522,33 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K63" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4557,33 +4557,33 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="K64" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4592,33 +4592,33 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>227</v>
+        <v>185</v>
       </c>
       <c r="K65" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>334</v>
+        <v>186</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>25</v>
@@ -4627,33 +4627,33 @@
         <v>3</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="K66" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>160</v>
+        <v>334</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>25</v>
@@ -4662,26 +4662,59 @@
         <v>3</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I67" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K67" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="J67" s="3" t="s">
+      <c r="B68" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="K67" s="3">
-        <v>9</v>
+      <c r="J68" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K68" s="3">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K67"/>
+  <autoFilter ref="A1:K68"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4749,6 +4782,7 @@
     <hyperlink ref="I65" r:id="rId64"/>
     <hyperlink ref="I66" r:id="rId65"/>
     <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4756,8 +4790,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4779,10 +4813,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4790,167 +4824,190 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>79</v>
+        <v>179</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>127</v>
+        <v>206</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="3">
         <v>26</v>
       </c>
-      <c r="D4" s="3">
-        <v>44</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>129</v>
+        <v>207</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>130</v>
+        <v>208</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>131</v>
+        <v>226</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>227</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>134</v>
+        <v>229</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>135</v>
+        <v>230</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>273</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>200</v>
+        <v>274</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>245</v>
+        <v>288</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>246</v>
+        <v>289</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
+        <v>6</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3">
         <v>3</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>76</v>
+      <c r="E9" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G8"/>
+  <autoFilter ref="A1:G9"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4959,6 +5016,7 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
+    <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4984,10 +5042,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B2" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>342</v>
@@ -4995,10 +5053,10 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B3" s="3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>343</v>
@@ -5006,18 +5064,18 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>303</v>
+        <v>344</v>
       </c>
       <c r="B4" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="B5" s="3">
         <v>26</v>
@@ -5039,10 +5097,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>307</v>
+        <v>238</v>
       </c>
       <c r="B7" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>349</v>
@@ -5050,10 +5108,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="B8" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>350</v>
@@ -5061,7 +5119,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="B9" s="3">
         <v>19</v>
@@ -5072,21 +5130,21 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>252</v>
+        <v>352</v>
       </c>
       <c r="B10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>353</v>
+        <v>254</v>
       </c>
       <c r="B11" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>354</v>
@@ -5097,7 +5155,7 @@
         <v>355</v>
       </c>
       <c r="B12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>356</v>
@@ -5119,7 +5177,7 @@
         <v>359</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>360</v>
@@ -5141,7 +5199,7 @@
         <v>363</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>364</v>
@@ -5186,7 +5244,7 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>368</v>
@@ -5197,7 +5255,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>369</v>
@@ -5269,7 +5327,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>375</v>

--- a/reports/devops-juniors-israel-2026-W29.xlsx
+++ b/reports/devops-juniors-israel-2026-W29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-16T08:29:36</t>
+    <t xml:space="preserve">2026-07-17T08:25:19</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -181,6 +181,24 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4438720783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -196,919 +214,877 @@
     <t xml:space="preserve">2026-05-24</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4440575333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eToro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claroty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4441499292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-maytronics-4440693288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior QA Engineer - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binyamina, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-qa-engineer-student-position-at-fives-4436801163</t>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IOT student tester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motorola Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/iot-student-tester-at-motorola-solutions-4434451222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator – Advanced Data Center and AI Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-%E2%80%93-advanced-data-center-and-ai-infrastructure-at-nvidia-4428415454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L3 Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/l3-support-engineer-at-nebius-4437652850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-at-paragon-4417886377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+    <t xml:space="preserve">Avionics Systems Engineering Student</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
   </si>
   <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412563583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist - Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gambit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, CI/CD, Git, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-student-position-at-gambit-security-4436034876</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician (Contractor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edwards Lifesciences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4438737325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UR Tech Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425556403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Help Desk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octally Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-help-desk-at-octally-integration-4438080376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-06</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menora Mivtachim Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GTM Engineer - Student Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oak - Identity Security OS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/gtm-engineer-student-role-at-oak-identity-security-os-4441425975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spinomenal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Science Student for AI Solutions Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-science-student-for-ai-solutions-group-at-intel-4439417170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - JB-651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system%C2%A0administrator-jb-651-at-pwc-israel-4429917341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412574130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4406043821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+    <t xml:space="preserve">‫Technical Support Representative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JobsSeek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representative-at-jobsseek-4430394705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-consist-4438704655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (Contractor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwards Lifesciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCLTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">תמיכה טכנית</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StoreNext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425560386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SW System Engineer for Naval Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-system-engineer-for-naval-systems-at-elbit-systems-israel-4437266128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Specialist (36911)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-36911-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439732218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Help Desk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octally Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-help-desk-at-octally-integration-4438080376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (36097)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-36097-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4439712914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Technical Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representative-at-jobsseek-4430394705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1269,7 +1245,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -1277,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1285,7 +1261,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -1293,7 +1269,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10">
@@ -1375,7 +1351,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
@@ -1391,7 +1367,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1401,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
@@ -1562,7 +1538,7 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1571,16 +1547,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1588,13 +1564,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
@@ -1652,31 +1628,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
+        <v>74</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1684,31 +1660,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1716,31 +1692,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1748,31 +1724,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -1780,31 +1756,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F11" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -1812,31 +1788,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -1844,31 +1820,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1876,31 +1852,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -1908,31 +1884,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -1940,31 +1916,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="17">
@@ -1972,31 +1948,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" s="3">
+        <v>44</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F17" s="3">
-        <v>51</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -2004,31 +1980,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="3">
+        <v>44</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>47</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="19">
@@ -2036,31 +2012,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20">
@@ -2068,31 +2044,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -2100,31 +2076,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -2132,31 +2108,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -2164,31 +2140,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
@@ -2196,31 +2172,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25">
@@ -2228,31 +2204,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
@@ -2260,31 +2236,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2323,7 +2299,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2337,7 +2313,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2352,22 +2328,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2">
@@ -2390,7 +2366,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>31</v>
@@ -2402,7 +2378,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
@@ -2425,7 +2401,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2437,7 +2413,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -2448,7 +2424,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2457,33 +2433,33 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
@@ -2495,7 +2471,7 @@
         <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2507,7 +2483,7 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -2530,7 +2506,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
@@ -2542,952 +2518,952 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
+        <v>74</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K7" s="3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="3">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K9" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11" s="3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K12" s="3">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K13" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>107</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K14" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="K15" s="3">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="K16" s="3">
-        <v>16</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="3">
+        <v>44</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="3">
-        <v>51</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="K17" s="3">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>47</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K18" s="3">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K19" s="3">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K20" s="3">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="K21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>146</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>62</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="K22" s="3">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="K23" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K24" s="3">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E25" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K26" s="3">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>66</v>
+        <v>176</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>62</v>
+        <v>187</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="K29" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>188</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="K30" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="K31" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>55</v>
+        <v>197</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="K32" s="3">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="K33" s="3">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -3498,19 +3474,19 @@
         <v>206</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
@@ -3519,10 +3495,10 @@
         <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -3533,276 +3509,276 @@
         <v>210</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="K35" s="3">
-        <v>28</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>99</v>
+        <v>219</v>
       </c>
       <c r="K36" s="3">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>90</v>
+        <v>224</v>
       </c>
       <c r="K37" s="3">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="K38" s="3">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>85</v>
+        <v>224</v>
       </c>
       <c r="K39" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>13</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>17</v>
-      </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>234</v>
+        <v>180</v>
       </c>
       <c r="K40" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K41" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>13</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="G42" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>242</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K42" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43">
@@ -3810,150 +3786,150 @@
         <v>243</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>151</v>
+        <v>244</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E43" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K43" s="3">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>191</v>
+        <v>248</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>192</v>
+        <v>249</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>204</v>
+        <v>252</v>
       </c>
       <c r="K44" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>250</v>
+        <v>137</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="K45" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>151</v>
+        <v>258</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>250</v>
+        <v>74</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E46" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="K46" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>258</v>
+        <v>98</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3962,33 +3938,33 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K47" s="3">
-        <v>53</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>261</v>
+        <v>72</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3997,22 +3973,22 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>265</v>
+        <v>65</v>
       </c>
       <c r="K48" s="3">
-        <v>23</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
@@ -4020,92 +3996,92 @@
         <v>266</v>
       </c>
       <c r="B49" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="3">
-        <v>10</v>
-      </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>271</v>
+        <v>169</v>
       </c>
       <c r="K49" s="3">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3">
+        <v>6</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="3">
-        <v>10</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="J50" s="3" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="K50" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>81</v>
+        <v>274</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>275</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>276</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>31</v>
@@ -4114,33 +4090,33 @@
         <v>277</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>59</v>
+        <v>278</v>
       </c>
       <c r="K51" s="3">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>279</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E52" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>31</v>
@@ -4149,56 +4125,56 @@
         <v>280</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>281</v>
+        <v>60</v>
       </c>
       <c r="K52" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="3">
+        <v>6</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" s="3">
-        <v>10</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>285</v>
+        <v>77</v>
       </c>
       <c r="K53" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>287</v>
+        <v>56</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>228</v>
+        <v>57</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4207,208 +4183,208 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K54" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="3">
+        <v>4</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="G55" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="3">
-        <v>6</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>293</v>
-      </c>
       <c r="J55" s="3" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K55" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E56" s="3">
+        <v>4</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="G56" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I56" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="3">
-        <v>6</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>297</v>
-      </c>
       <c r="J56" s="3" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="K56" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>300</v>
+        <v>166</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" s="3">
         <v>4</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="K57" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>303</v>
+        <v>192</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>139</v>
+        <v>57</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K58" s="3">
         <v>4</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="K58" s="3">
-        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>151</v>
+        <v>304</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="K59" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>139</v>
+        <v>309</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>25</v>
@@ -4420,30 +4396,30 @@
         <v>310</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="K60" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>25</v>
@@ -4452,33 +4428,33 @@
         <v>3</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>185</v>
+        <v>315</v>
       </c>
       <c r="K61" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>215</v>
+        <v>131</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4487,33 +4463,33 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>185</v>
+        <v>219</v>
       </c>
       <c r="K62" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>215</v>
+        <v>137</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4522,33 +4498,33 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="K63" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>328</v>
+        <v>131</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4557,19 +4533,19 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="K64" s="3">
         <v>0</v>
@@ -4577,13 +4553,13 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4592,129 +4568,59 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="K65" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>332</v>
+        <v>221</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>163</v>
+        <v>226</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E66" s="3">
-        <v>3</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>310</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="K66" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E67" s="3">
-        <v>3</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="K67" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E68" s="3">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K68" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K68"/>
+  <autoFilter ref="A1:K66"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4781,8 +4687,6 @@
     <hyperlink ref="I64" r:id="rId63"/>
     <hyperlink ref="I65" r:id="rId64"/>
     <hyperlink ref="I66" r:id="rId65"/>
-    <hyperlink ref="I67" r:id="rId66"/>
-    <hyperlink ref="I68" r:id="rId67"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4791,8 +4695,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -4813,10 +4717,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -4824,148 +4728,148 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>205</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>206</v>
+        <v>141</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>207</v>
+        <v>143</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>208</v>
+        <v>144</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>226</v>
+        <v>185</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>274</v>
+        <v>196</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>289</v>
+        <v>246</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -4974,40 +4878,63 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>326</v>
+        <v>292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>327</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="3">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="3">
         <v>3</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>85</v>
+      <c r="E10" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -5017,6 +4944,7 @@
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
     <hyperlink ref="F9" r:id="rId8"/>
+    <hyperlink ref="F10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5031,178 +4959,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B2" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B4" s="3">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B5" s="3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="B6" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="B7" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B8" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>324</v>
+        <v>217</v>
       </c>
       <c r="B9" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="B10" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>254</v>
+        <v>345</v>
       </c>
       <c r="B11" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="B12" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5222,10 +5150,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2">
@@ -5233,10 +5161,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3">
@@ -5247,7 +5175,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
@@ -5255,10 +5183,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5">
@@ -5269,7 +5197,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6">
@@ -5280,7 +5208,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5301,13 +5229,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2">
@@ -5318,7 +5246,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5327,22 +5255,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W29.xlsx
+++ b/reports/devops-juniors-israel-2026-W29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="387">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-17T08:25:19</t>
+    <t xml:space="preserve">2026-07-19T08:32:45</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -181,829 +181,889 @@
     <t xml:space="preserve">2026-06-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Cloud Operations Engineer</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoqneam Illit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-ai-4430612805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autobrains Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anecdotes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-anecdotes-4429933095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator VMware (36310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, Virtualization, Active Directory, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-vmware-36310-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4441455499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Corp System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer - Intern position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Align Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer - Unmanned Maritime Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-unmanned-maritime-systems-at-elbit-systems-israel-4433797145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist -Temporary Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finonex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-finonex-4431501925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droxi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4441499292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menora Mivtachim Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-menora-mivtachim-group-4434972024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prisma Photonics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk (student position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LiveU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Tier 2 - 240769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Monitoring, Virtualization, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-tier-2-240769-at-experis-israel-4434811963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maytronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yizra'el, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-maytronics-4440693288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Navina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-navina-4397936369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal Security Systems (India) Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magal, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Databases, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-technician-at-magal-security-systems-india-ltd-4442431214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-operations-engineer-at-final-4435822603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safer Place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-support-engineer-at-safer-place-4437083465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airobotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForSight Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-at-forsight-robotics-4438498013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer (R&amp;D Environments)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-r-d-environments-at-abra-4434113221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineering Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-tier-1-at-cato-networks-4434573124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulation and Algorithms System Engineer (ITB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/simulation-and-algorithms-system-engineer-itb-at-elbit-systems-israel-4431512384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISL Global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELP DESK TIER ONE 241758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-tier-one-241758-at-experis-4439208565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk (Temporary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst – Hebrew Language Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-%E2%80%93-hebrew-language-support-at-hcltech-4435566860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RealPlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tnuva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoreNext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-at-storenext-4438985234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
   </si>
   <si>
     <t xml:space="preserve">Confidential Careers</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-operations-engineer-at-confidential-careers-4438720783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), CI/CD, Git, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-nvidia-4433428247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autobrains Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), Docker, Git, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-autobrains-technologies-4440209390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Git, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4437695096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allpha Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, CI/CD, Networking, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-allpha-innovation-4439809639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4440575333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Emulation Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-emulation-engineer-university-graduate-google-cloud-at-google-4414165506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computer System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eToro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), CI/CD, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-etoro-4434952696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8533931002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmit Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-transmit-security-4409875183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Corp System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/7916835/?gh_jid=7916835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations &amp; Helpdesk Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claroty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Azure, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-helpdesk-engineer-at-claroty-4412805136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer - Intern position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Align Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, AWS, Cloud (any), Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-intern-position-at-align-technology-4303646784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Droxi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-operations-engineer-at-droxi-4426788584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-comblack-4441499292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk (student position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LiveU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-student-position-at-liveu-4434277505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Temporary Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Monitoring, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-temporary-position-at-prisma-photonics-4438989683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-yael-korentec-technologies-4431373486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Network Operations Center Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-network-operations-center-engineer-at-extreme-4416668921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (1006801)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elad Software Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4438193563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk Specialist #1344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Networking, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-specialist-%231344-at-rad-4430443104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
+    <t xml:space="preserve">Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Helpdesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSC Sports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Log-On Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4438737325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Service Specialist - Tier 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-service-specialist-tier-1-at-solaredge-technologies-4408365748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SW System Engineer for Naval Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sw-system-engineer-for-naval-systems-at-elbit-systems-israel-4437266128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flex</t>
   </si>
   <si>
     <t xml:space="preserve">Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Modiin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-modiin-at-nebius-4437655752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maytronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yizra'el, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-maytronics-4440693288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4437013944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nova Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4413884631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avionics Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/avionics-systems-engineering-student-at-elbit-systems-israel-4412563583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineering-student-at-elbit-systems-israel-4405545785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student for Strength and Dynamics Analysis team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-for-strength-and-dynamics-analysis-team-at-elbit-systems-israel-4421930557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-liveu-4429912440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-technician-at-unilink-ltd-4440911956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desktop Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISL Global</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/desktop-support-specialist-at-sisl-global-4440959535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk (Temporary)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-temporary-at-personetics-4428653392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Technician (Contractor)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edwards Lifesciences</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-technician-contractor-at-edwards-lifesciences-4435668433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4430592021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-sisl-global-4440963700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RealPlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-specialist-at-realplay-4415648752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-student-at-elbit-systems-israel-4435662496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4395665709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WSC Sports</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-wsc-sports-4415703367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-log-on-software-4438737325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tnuva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/field-it-support-specialist-at-tnuva-4438464877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician (Part-Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-part-time-at-confidential-careers-4437264418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/Systems Engineer: Offensive Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UR Tech Jobs</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulwarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiberias, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-genie-4438491899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oktopost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Specialist (Help Desk)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octally Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-help-desk-at-octally-integration-4438080376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WalkMe</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-systems-engineer-offensive-cybersecurity-at-ur-tech-jobs-4425556403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-student-position-at-confidential-4437273184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phibro Middle East &amp; Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-phibro-middle-east-europe-4439142494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist (Help Desk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octally Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-help-desk-at-octally-integration-4438080376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulwarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-bulwarx-4435101187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oktopost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-oktopost-4436981915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‫Technical Support Representative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JobsSeek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%E2%80%ABtechnical-support-representative-at-jobsseek-4430394705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4439716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-consist-4438704655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Support Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-flex-4436841213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineering Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineering-student-at-elbit-systems-israel-4414854587</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-walkme-4374713618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">תמיכה טכנית - מערכת Meteor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%9E%D7%A2%D7%A8%D7%9B%D7%AA-meteor-at-storenext-4440240961</t>
   </si>
   <si>
     <t xml:space="preserve">Skill</t>
@@ -1042,24 +1102,18 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
@@ -1069,22 +1123,22 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1245,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -1253,7 +1307,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1261,7 +1315,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -1269,7 +1323,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10">
@@ -1351,7 +1405,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
@@ -1359,7 +1413,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1367,7 +1421,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1401,7 +1455,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
@@ -1421,7 +1475,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1538,7 +1592,7 @@
         <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>26</v>
@@ -1547,16 +1601,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1564,19 +1618,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>63</v>
@@ -1596,13 +1650,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
@@ -1611,16 +1665,16 @@
         <v>76</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -1628,13 +1682,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>25</v>
@@ -1643,16 +1697,16 @@
         <v>74</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -1660,13 +1714,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>27</v>
@@ -1675,16 +1729,16 @@
         <v>70</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1692,31 +1746,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="3">
+        <v>68</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3">
-        <v>64</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1724,31 +1778,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="3">
+        <v>64</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
-        <v>61</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -1756,13 +1810,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>28</v>
@@ -1771,16 +1825,16 @@
         <v>57</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -1788,31 +1842,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3">
-        <v>56</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -1820,31 +1874,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="3">
+        <v>47</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>52</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="14">
@@ -1852,31 +1906,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="3">
+        <v>44</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="3">
-        <v>51</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -1884,31 +1938,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>40</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
-        <v>47</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="16">
@@ -1916,31 +1970,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
@@ -1948,31 +2002,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="18">
@@ -1980,31 +2034,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -2012,7 +2066,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>130</v>
@@ -2024,7 +2078,7 @@
         <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>132</v>
@@ -2044,13 +2098,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
@@ -2059,16 +2113,16 @@
         <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -2076,31 +2130,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F21" s="3">
+        <v>30</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3">
-        <v>32</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -2146,7 +2200,7 @@
         <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>25</v>
@@ -2155,16 +2209,16 @@
         <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24">
@@ -2172,31 +2226,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
@@ -2204,13 +2258,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>26</v>
@@ -2228,7 +2282,7 @@
         <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
@@ -2236,13 +2290,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>26</v>
@@ -2299,8 +2353,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2378,7 +2432,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -2413,7 +2467,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -2424,7 +2478,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>26</v>
@@ -2433,39 +2487,39 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>63</v>
@@ -2483,18 +2537,18 @@
         <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
@@ -2503,7 +2557,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>175</v>
@@ -2512,24 +2566,24 @@
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K6" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
@@ -2538,7 +2592,7 @@
         <v>74</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>175</v>
@@ -2547,24 +2601,24 @@
         <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>27</v>
@@ -2573,7 +2627,7 @@
         <v>70</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>175</v>
@@ -2582,80 +2636,80 @@
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K8" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="3">
+        <v>68</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3">
-        <v>64</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="K9" s="3">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3">
+        <v>64</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>61</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -2663,13 +2717,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="C11" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>28</v>
@@ -2678,182 +2732,182 @@
         <v>57</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="K11" s="3">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="3">
-        <v>56</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K12" s="3">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>47</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>52</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>106</v>
-      </c>
       <c r="K13" s="3">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3">
+        <v>44</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="3">
-        <v>51</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="K14" s="3">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>40</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3">
-        <v>47</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="K15" s="3">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>175</v>
@@ -2862,68 +2916,68 @@
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K16" s="3">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="K17" s="3">
-        <v>59</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>175</v>
@@ -2932,18 +2986,18 @@
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K18" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>130</v>
@@ -2955,7 +3009,7 @@
         <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>132</v>
@@ -2973,18 +3027,18 @@
         <v>134</v>
       </c>
       <c r="K19" s="3">
-        <v>58</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
@@ -2993,57 +3047,57 @@
         <v>32</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="K20" s="3">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>30</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="3">
-        <v>32</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="K21" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -3078,7 +3132,7 @@
         <v>150</v>
       </c>
       <c r="K22" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -3089,7 +3143,7 @@
         <v>152</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>25</v>
@@ -3098,7 +3152,7 @@
         <v>30</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>175</v>
@@ -3107,33 +3161,33 @@
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>61</v>
+        <v>157</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>175</v>
@@ -3142,24 +3196,24 @@
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>159</v>
+        <v>89</v>
       </c>
       <c r="K24" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>26</v>
@@ -3180,21 +3234,21 @@
         <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="K25" s="3">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>26</v>
@@ -3218,7 +3272,7 @@
         <v>169</v>
       </c>
       <c r="K26" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -3229,13 +3283,13 @@
         <v>177</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>178</v>
@@ -3250,27 +3304,27 @@
         <v>179</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="K27" s="3">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>183</v>
@@ -3285,10 +3339,10 @@
         <v>184</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="K28" s="3">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -3299,7 +3353,7 @@
         <v>186</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
@@ -3308,77 +3362,77 @@
         <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J29" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" s="3">
         <v>60</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="C30" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" s="3">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>175</v>
@@ -3387,10 +3441,10 @@
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="K31" s="3">
         <v>0</v>
@@ -3398,48 +3452,48 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
         <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>95</v>
+        <v>204</v>
       </c>
       <c r="K32" s="3">
-        <v>63</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
@@ -3448,7 +3502,7 @@
         <v>17</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>175</v>
@@ -3457,24 +3511,24 @@
         <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>169</v>
       </c>
       <c r="K33" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>25</v>
@@ -3483,7 +3537,7 @@
         <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>175</v>
@@ -3492,33 +3546,33 @@
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>86</v>
+        <v>169</v>
       </c>
       <c r="K34" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>211</v>
+        <v>112</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>175</v>
@@ -3527,48 +3581,48 @@
         <v>31</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>95</v>
+        <v>215</v>
       </c>
       <c r="K35" s="3">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>219</v>
+        <v>89</v>
       </c>
       <c r="K36" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3576,42 +3630,42 @@
         <v>220</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>17</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E37" s="3">
-        <v>13</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
+      <c r="J37" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>224</v>
-      </c>
       <c r="K37" s="3">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>221</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>226</v>
@@ -3623,33 +3677,33 @@
         <v>13</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="K38" s="3">
-        <v>53</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>221</v>
+        <v>117</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>27</v>
@@ -3658,7 +3712,7 @@
         <v>13</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>175</v>
@@ -3667,33 +3721,33 @@
         <v>31</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>224</v>
+        <v>48</v>
       </c>
       <c r="K39" s="3">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3">
         <v>13</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>175</v>
@@ -3702,24 +3756,24 @@
         <v>31</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="K40" s="3">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3728,7 +3782,7 @@
         <v>13</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>175</v>
@@ -3737,129 +3791,129 @@
         <v>31</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K41" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E42" s="3">
+        <v>13</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="K42" s="3">
         <v>10</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K42" s="3">
-        <v>54</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>243</v>
+        <v>185</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E43" s="3">
-        <v>10</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="K43" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="G44" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E44" s="3">
-        <v>10</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>251</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="K44" s="3">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>25</v>
@@ -3868,33 +3922,33 @@
         <v>10</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>256</v>
+        <v>59</v>
       </c>
       <c r="K45" s="3">
-        <v>5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>25</v>
@@ -3903,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>175</v>
@@ -3912,24 +3966,24 @@
         <v>31</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="K46" s="3">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>25</v>
@@ -3938,7 +3992,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>175</v>
@@ -3950,21 +4004,21 @@
         <v>262</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="K47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>72</v>
+        <v>263</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>25</v>
@@ -3973,7 +4027,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>175</v>
@@ -3985,10 +4039,10 @@
         <v>265</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="K48" s="3">
-        <v>54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3996,19 +4050,19 @@
         <v>266</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E49" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>175</v>
@@ -4017,33 +4071,33 @@
         <v>31</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="K49" s="3">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>192</v>
+        <v>272</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>271</v>
+        <v>136</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>175</v>
@@ -4052,33 +4106,33 @@
         <v>31</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>65</v>
+        <v>275</v>
       </c>
       <c r="K50" s="3">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>274</v>
+        <v>69</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>137</v>
+        <v>71</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E51" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>175</v>
@@ -4087,33 +4141,33 @@
         <v>31</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>278</v>
+        <v>59</v>
       </c>
       <c r="K51" s="3">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>279</v>
+        <v>117</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>57</v>
+        <v>280</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E52" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>175</v>
@@ -4122,24 +4176,24 @@
         <v>31</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>60</v>
+        <v>169</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>25</v>
@@ -4148,7 +4202,7 @@
         <v>6</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>175</v>
@@ -4157,24 +4211,24 @@
         <v>31</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>56</v>
+        <v>288</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>25</v>
@@ -4183,7 +4237,7 @@
         <v>6</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>175</v>
@@ -4192,10 +4246,10 @@
         <v>31</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="K54" s="3">
         <v>3</v>
@@ -4203,57 +4257,57 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>289</v>
+        <v>86</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="K55" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>292</v>
+        <v>180</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>74</v>
+        <v>296</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>175</v>
@@ -4262,33 +4316,33 @@
         <v>31</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K56" s="3">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>175</v>
@@ -4297,33 +4351,33 @@
         <v>31</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="K57" s="3">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>175</v>
@@ -4332,33 +4386,33 @@
         <v>31</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="K58" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>305</v>
+        <v>51</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>175</v>
@@ -4367,68 +4421,68 @@
         <v>31</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>77</v>
+        <v>308</v>
       </c>
       <c r="K59" s="3">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>175</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="K60" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>313</v>
+        <v>117</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>137</v>
+        <v>315</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E61" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>175</v>
@@ -4437,24 +4491,24 @@
         <v>31</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>315</v>
+        <v>215</v>
       </c>
       <c r="K61" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>131</v>
+        <v>320</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>25</v>
@@ -4463,7 +4517,7 @@
         <v>3</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>175</v>
@@ -4472,24 +4526,24 @@
         <v>31</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>219</v>
+        <v>79</v>
       </c>
       <c r="K62" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>137</v>
+        <v>101</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>25</v>
@@ -4498,7 +4552,7 @@
         <v>3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>175</v>
@@ -4507,24 +4561,24 @@
         <v>31</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="K63" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>131</v>
+        <v>328</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>25</v>
@@ -4533,7 +4587,7 @@
         <v>3</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>175</v>
@@ -4542,24 +4596,24 @@
         <v>31</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>60</v>
+        <v>223</v>
       </c>
       <c r="K64" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>187</v>
+        <v>332</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>25</v>
@@ -4568,7 +4622,7 @@
         <v>3</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>175</v>
@@ -4577,50 +4631,192 @@
         <v>31</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K65" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>328</v>
+        <v>180</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>221</v>
+        <v>335</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>226</v>
+        <v>86</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E66" s="3">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K66" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="3">
+        <v>3</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="K67" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K68" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="3">
+        <v>3</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="K69" s="3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K66" s="3">
-        <v>53</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K66"/>
+  <autoFilter ref="A1:K70"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -4687,6 +4883,10 @@
     <hyperlink ref="I64" r:id="rId63"/>
     <hyperlink ref="I65" r:id="rId64"/>
     <hyperlink ref="I66" r:id="rId65"/>
+    <hyperlink ref="I67" r:id="rId66"/>
+    <hyperlink ref="I68" r:id="rId67"/>
+    <hyperlink ref="I69" r:id="rId68"/>
+    <hyperlink ref="I70" r:id="rId69"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4694,8 +4894,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="37" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -4728,213 +4928,167 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>158</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>144</v>
+        <v>198</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>195</v>
+        <v>256</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>243</v>
+        <v>330</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>244</v>
+        <v>331</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>245</v>
+        <v>333</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>246</v>
+        <v>334</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>272</v>
+        <v>316</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="3">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
@@ -4943,8 +5097,6 @@
     <hyperlink ref="F6" r:id="rId5"/>
     <hyperlink ref="F7" r:id="rId6"/>
     <hyperlink ref="F8" r:id="rId7"/>
-    <hyperlink ref="F9" r:id="rId8"/>
-    <hyperlink ref="F10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -4959,178 +5111,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B2" s="3">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>298</v>
+        <v>324</v>
       </c>
       <c r="B3" s="3">
         <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="B4" s="3">
         <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>336</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>337</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>338</v>
+        <v>358</v>
       </c>
       <c r="B6" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="B7" s="3">
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>294</v>
+        <v>346</v>
       </c>
       <c r="B8" s="3">
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>217</v>
+        <v>362</v>
       </c>
       <c r="B9" s="3">
         <v>17</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3">
         <v>15</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>344</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>345</v>
+        <v>247</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>346</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B15" s="3">
         <v>6</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -5150,10 +5302,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2">
@@ -5161,10 +5313,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -5172,10 +5324,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -5183,10 +5335,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5">
@@ -5197,7 +5349,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6">
@@ -5208,7 +5360,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -5229,13 +5381,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2">
@@ -5246,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -5255,22 +5407,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="D4" s="3"/>
     </row>
